--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0228.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0228.xlsx
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Một cô gái đến từ Hồng Trấn tên là Shicheng muốn thực hiện Nghi Lễ Dâng Tặng, nhưng cô bị tấn công bởi bọn TD. Bạn kịp thời cứu cô thoát khỏi nguy hiểm.</t>
+          <t>Một cô gái đến từ Hongzhen tên là Shicheng muốn thực hiện Nghi Lễ Dâng Tặng, nhưng cô bị tấn công bởi bọn TD. Bạn kịp thời cứu cô thoát khỏi nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Tài nguyên cốt truyện trước sẽ không được sử dụng lại. Có thể xóa toàn bộ video từ các quest trước đó.</t>
+          <t>Tài nguyên cốt truyện cũ sẽ không được sử dụng lại. Toàn bộ video từ nhiệm vụ trước có thể xóa bỏ.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Clear Resources ({0}/{1})</t>
+          <t>Thanh Tẩy Tài Nguyên ({0}/{1})</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Kết thúc ngay bây giờ sẽ &lt;color=#d8a22f&gt;fails the challenge&lt;/color&gt;. Xác nhận kết thúc và hoàn thành thử thách?</t>
+          <t>Kết thúc ngay bây giờ sẽ &lt;color=#d8a22f&gt;thất bại thử thách&lt;/color&gt;. Xác nhận kết thúc và hoàn thành thử thách?</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Xác nhận &lt;color=#d8a22f&gt;your current points&lt;/color&gt; và kết thúc thử thách ngay bây giờ?</t>
+          <t>Xác nhận &lt;color=#d8a22f&gt;điểm hiện tại&lt;/color&gt; và kết thúc thử thách ngay bây giờ?</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Cộng Hưởng Giả 20</t>
+          <t>Mở khóa ở Cấp Resonator 20</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Thời gian còn lại của Pioneer Podcast hiện tại là &lt;color=#c49e55&gt;less than 3 days&lt;/color&gt;. Cậu có muốn tiếp tục mua không?</t>
+          <t>Thời gian còn lại của Pioneer Podcast hiện tại là &lt;color=#c49e55&gt;dưới 3 ngày&lt;/color&gt;. Cậu có muốn tiếp tục mua không?</t>
         </is>
       </c>
     </row>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Kênh &lt;color=#c49e55&gt;Insider Channel&lt;/color&gt; của Pioneer Podcast đã được mở khóa, vật phẩm này không thể sử dụng được nữa.</t>
+          <t>Kênh &lt;color=#c49e55&gt;Insider&lt;/color&gt; của Pioneer Podcast đã được mở khóa, vật phẩm này không thể sử dụng được nữa.</t>
         </is>
       </c>
     </row>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng vật phẩm này, bạn có thể mở khóa &lt;color=#c49e55&gt;Insider Channel&lt;/color&gt; của Pioneer Podcast.</t>
+          <t>Sau khi sử dụng vật phẩm này, bạn có thể mở khóa &lt;color=#c49e55&gt;Kênh Nội Bộ&lt;/color&gt; của Pioneer Podcast.</t>
         </is>
       </c>
     </row>
@@ -19166,7 +19166,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Kênh &lt;color=#c49e55&gt;Connoisseur Channel&lt;/color&gt; của Pioneer Podcast đã được mở khóa, vật phẩm này không thể sử dụng được nữa.</t>
+          <t>Kênh &lt;color=#c49e55&gt;Connoisseur&lt;/color&gt; của Pioneer Podcast đã được mở khóa, vật phẩm này không thể sử dụng được nữa.</t>
         </is>
       </c>
     </row>
@@ -19231,7 +19231,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng vật phẩm này, cậu có thể mở khóa kênh &lt;color=#c49e55&gt;Connoisseur Channel&lt;/color&gt; của Pioneer Podcast.</t>
+          <t>Sau khi sử dụng vật phẩm này, cậu có thể mở khóa kênh &lt;color=#c49e55&gt;Connoisseur&lt;/color&gt; của Pioneer Podcast.</t>
         </is>
       </c>
     </row>
@@ -19621,7 +19621,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>R?i ?i à?</t>
+          <t>Cút đi à?</t>
         </is>
       </c>
     </row>
@@ -21376,7 +21376,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Bạn có muốn vào mô phỏng với Cộng Hưởng Giả hiện tại và vũ khí khởi đầu của họ không?</t>
+          <t>Bạn có muốn vào mô phỏng với Resonator hiện tại và vũ khí khởi đầu của họ không?</t>
         </is>
       </c>
     </row>
@@ -22091,7 +22091,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Namipon này đang được một Cộng Hưởng Giả khác sử dụng. Ngươi có muốn điều chỉnh không?</t>
+          <t>Namipon này đang được một Resonator khác sử dụng. Ngươi có muốn điều chỉnh không?</t>
         </is>
       </c>
     </row>
@@ -22678,7 +22678,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>R?i ?i à?</t>
+          <t>Cút đi à?</t>
         </is>
       </c>
     </row>
@@ -28075,7 +28075,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Rover chưa được kích hoạt. Thao tác thất bại.</t>
+          <t>Vận Mệnh Giả chưa được kích hoạt. Thao tác thất bại.</t>
         </is>
       </c>
     </row>
@@ -28205,7 +28205,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Thuộc Tính Phụ Tiếng Vang Hiện Tại Không Tồn Tại</t>
+          <t>Thuộc Tính Phụ Echo Hiện Tại Không Tồn Tại</t>
         </is>
       </c>
     </row>
@@ -31130,7 +31130,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Bạn không thể đổi Cộng Hưởng Giả trong khu vực này.</t>
+          <t>Bạn không thể đổi Resonator trong khu vực này.</t>
         </is>
       </c>
     </row>
@@ -31195,7 +31195,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả đã chọn không hợp lệ</t>
+          <t>Resonator đã chọn không hợp lệ</t>
         </is>
       </c>
     </row>
